--- a/testdata/import/01-catalog.xlsx
+++ b/testdata/import/01-catalog.xlsx
@@ -426,19 +426,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="31" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,35 +460,40 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>ИТ-программа</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Номер договора</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Подписание лицензии</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Срок действия лицензии (год)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Статус по передачи</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ФИО Менеджера</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Ответственные от ВУЗа</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
@@ -509,27 +515,27 @@
           <t>Платформа онлайн-обучения</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>ДГ-2025-017</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Передано</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Петров Пётр Алексеевич</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Соловьёв Дмитрий Рашидович</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Вуз готовит заявку на продление</t>
         </is>
@@ -551,27 +557,27 @@
           <t>Песочница DevOps</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>ДГ-2026-047</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Петров Пётр Алексеевич</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Баранова Юлия Сергеевна</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Стенд разворачивают во втором компьютерном классе</t>
         </is>
@@ -593,22 +599,22 @@
           <t>Postgres Pro Enterprise</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>ДГ-2026-058</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Иванова Мария Сергеевна</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Гафурова Людмила Владимировна</t>
         </is>
@@ -630,33 +636,33 @@
           <t>Стенд киберполигона</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>ДГ-2026-012</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>46280</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>2027</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Передано</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Орлова Ольга Дмитриевна</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Марков Леонид Васильевич</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Лицензия продлена до конца 2027 года</t>
         </is>
@@ -680,31 +686,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Анализ защищённости приложений</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>ДГ-2026-201</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>46266</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>2027</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Смирнов Алексей Викторович</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Гусев Владимир Петрович</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Лаборатория анализа кода</t>
         </is>
@@ -728,28 +739,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Администратор баз данных PostgreSQL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>ДГ-2026-202</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>15.08.2026</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Передано</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Кузнецова Елена Андреевна</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Журавлёв Виталий Анатольевич</t>
         </is>
@@ -773,31 +789,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Администратор Linux</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>ДГ-2026-203</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>46254</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>2028</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Соколов Дмитрий Игоревич</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Тихонова Светлана Сергеевна</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Два компьютерных класса</t>
         </is>
@@ -821,26 +842,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Администратор Linux</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>ДГ-2026-203</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>46254</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>2028</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Соколов Дмитрий Игоревич</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Тихонова Светлана Сергеевна</t>
         </is>
@@ -864,28 +890,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Анализ защищённости приложений</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>ДГ-2026-204</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>03.09.2026</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>2027</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Попова Наталья Валерьевна</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Ершов Леонид Юрьевич</t>
         </is>
@@ -909,26 +940,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Python-разработчик</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>ДГ-2026-205</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>46183</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Передано</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Егорова Дарья Константиновна</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Тарасов Игорь Геннадьевич</t>
         </is>
@@ -952,31 +988,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>Инженер DevOps</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>ДГ-2026-206</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>46204</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>2027</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Приостановлено</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Павлов Кирилл Андреевич</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Воробьёв Григорий Олегович</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Вуз перенёс старт программы на весенний семестр</t>
         </is>
@@ -998,28 +1039,28 @@
           <t>Solar Dozor</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>ДГ-2026-207</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="F13" s="2" t="n">
         <v>46154</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="G13" s="2" t="n">
         <v>46568</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Передано</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Степанова Ирина Владимировна</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Калинин Леонид Петрович</t>
         </is>
@@ -1043,26 +1084,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>Администратор Linux</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>ДГ-2026-208</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="F14" s="2" t="n">
         <v>46270</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>2027</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Николаев Роман Сергеевич</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Мельников Николай Михайлович</t>
         </is>
@@ -1086,31 +1132,36 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>Java-разработчик</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>ДГ-2026-209</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="F15" s="2" t="n">
         <v>46275</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>2027</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Белова Ксения Александровна</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Борисова Наталья Михайловна</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Ждём список групп от вуза</t>
         </is>
@@ -1132,28 +1183,28 @@
           <t>MaxPatrol SIEM</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>ДГ-2026-210</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="F16" s="2" t="n">
         <v>46134</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>3</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Передано</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Фёдоров Виктор Геннадьевич</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Сафина Марина Викторовна</t>
         </is>
@@ -1177,26 +1228,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>Специалист по защите информации</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>ДГ-2026-211</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="F17" s="2" t="n">
         <v>46283</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>2027</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Захарова Светлана Юрьевна</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Ильина Вера Юрьевна</t>
         </is>
@@ -1220,31 +1276,36 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>Python-разработчик</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>ДГ-2026-212</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="F18" s="2" t="n">
         <v>46266</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>2027</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Петров Пётр Алексеевич</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Лаврова Ирина Сергеевна</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Первый договор с вузом</t>
         </is>
@@ -1268,26 +1329,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>Администратор Linux</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>ДГ-2026-213</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="F19" s="2" t="n">
         <v>46259</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>2027</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Передано</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Волков Андрей Михайлович</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Чернов Антон Викторович</t>
         </is>
@@ -1311,31 +1377,36 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>Администратор Linux</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>ДГ-2026-213</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="F20" s="2" t="n">
         <v>46259</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>2027</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Волков Андрей Михайлович</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Чернов Антон Викторович</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Новый вендор и продукт - появятся в справочниках</t>
         </is>
@@ -1359,28 +1430,33 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>Сетевой инженер</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>ДГ-2026-214</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>12.09.2026</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>2027</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Лебедев Игорь Николаевич</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Руденко Полина Андреевна</t>
         </is>
